--- a/data/judgements/GPT4.1_aae-vs-gemini-1.5-flash/Llama-3.3-70B-Instruct/better_model_topics_gpt-4.1_vs_gemini-1.5-flash.xlsx
+++ b/data/judgements/GPT4.1_aae-vs-gemini-1.5-flash/Llama-3.3-70B-Instruct/better_model_topics_gpt-4.1_vs_gemini-1.5-flash.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Topic</t>
   </si>
@@ -28,55 +28,25 @@
     <t>Representation</t>
   </si>
   <si>
-    <t>KeyBertInspired Representation</t>
-  </si>
-  <si>
-    <t>LLM Representation</t>
-  </si>
-  <si>
     <t>Representative_Docs</t>
   </si>
   <si>
-    <t>-1_specific_lacks_structure_details</t>
-  </si>
-  <si>
-    <t>0_message_message uses_similar message_suitable</t>
-  </si>
-  <si>
-    <t>1_grammatical errors_errors_grammatical_manner</t>
-  </si>
-  <si>
-    <t>['specific', 'lacks', 'structure', 'details', 'precision', 'manner', 'includes', 'grammatical', 'also', 'lacks precision']</t>
-  </si>
-  <si>
-    <t>['message', 'message uses', 'similar message', 'suitable', 'may suitable', 'language casual', 'casual tone', 'less accessible', 'credible', 'credible readers']</t>
-  </si>
-  <si>
-    <t>['grammatical errors', 'errors', 'grammatical', 'manner', 'quality', 'contains grammatical', 'overall', 'overall quality', 'language grammatical', 'information less']</t>
-  </si>
-  <si>
-    <t>['engaging story', 'contrast telling', 'telling specific', 'specific engaging', 'vague lacks', 'engaging', 'planning', 'language lacks', 'summary', 'lacks specific']</t>
-  </si>
-  <si>
-    <t>['written informal', 'language conversational', 'language casual', 'message uses', 'conversational tone', 'expressions slang', 'formal discussion', 'conversational', 'casual tone', 'colloquial tone']</t>
-  </si>
-  <si>
-    <t>['errors informal', 'answer contrast', 'grammatical errors', 'quality answer', 'language grammatical', 'contains informal', 'errors colloquial', 'manner grammatical', 'credibility contrast', 'although conveying']</t>
-  </si>
-  <si>
-    <t>['Language and Clarity']</t>
-  </si>
-  <si>
-    <t>['Informal language issues']</t>
-  </si>
-  <si>
-    <t>['In contrast, Answer1, while telling a specific and engaging story, is more limited in its applicability to other heroic animal stories due to', 'Answer1, on the other hand, uses informal language and lacks specific details about the planning process.', 'In contrast, Answer1, while telling a specific and engaging story, is more limited in its applicability to other heroic animal stories due to its specific details and lack of a broadly applicable structure.']</t>
-  </si>
-  <si>
-    <t>['In contrast, Answer1, while conveying a similar message, uses informal language and slang, which may not be appropriate for all audiences or settings.', 'In contrast, Answer2, while conveying a similar message, uses informal language and a more casual tone, which may not be as effective in conveying the importance of recycling to all audiences.', 'In contrast, Answer1, while conveying a similar message, uses informal language and slang, which may make it less accessible or credible to some readers.']</t>
-  </si>
-  <si>
-    <t>['Answer1, while conveying the same information, contains informal language, grammatical errors, and colloquial expressions that detract from its overall quality and clarity.', 'In contrast, Answer1 uses informal language and contains grammatical errors, which detract from the overall quality of the answer.', 'In contrast, Answer1 uses informal language and contains grammatical errors, which detract from its overall quality.']</t>
+    <t>0_Informal Language Usage</t>
+  </si>
+  <si>
+    <t>1_Slang clarity concerns</t>
+  </si>
+  <si>
+    <t>['Informal Language Usage']</t>
+  </si>
+  <si>
+    <t>['Slang clarity concerns']</t>
+  </si>
+  <si>
+    <t>['conveying the same information uses informal language', 'conveying similar information uses colloquial language', 'conveying similar information uses informal language']</t>
+  </si>
+  <si>
+    <t>['slang which may make the explanation less clear', 'slang which may make it less accessible', 'slang which may make it less clear']</t>
   </si>
 </sst>
 </file>
@@ -434,10 +404,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,80 +423,39 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>434</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>-1</v>
-      </c>
-      <c r="B2">
-        <v>107</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>49</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
